--- a/stories/arbres/ATOM-SEC.RUE.002-06.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.002-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Cédric va au marché. Il marche avec maman. Maman est l'adulte. Ils arrivent au bord. Cédric donne la main. La main est dans la main. Les pieds restent sur le trottoir. Ils restent sur le trottoir en attendant. Maman dit : on attend le feu vert. Cédric sent la main. Il reste près de maman. Le feu est vert. Maman dit : feu vert. On avance avec l'adulte. Cédric tient la main. Ils marchent ensemble. L'adulte est là. Cédric dit : merci maman.</t>
+          <t>Cédric va au marché. Il marche avec maman. Maman est l'adulte. Ils arrivent au bord. Cédric donne la main. La main est dans la main. Les pieds restent sur le trottoir. Ils restent sur le trottoir en attendant. On attend le feu vert. Cédric sent la main. Il reste près de maman. Le feu est vert. Feu vert. On avance avec l'adulte. Cédric tient la main. Ils marchent ensemble. L'adulte est là. Merci maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Cédric va au marché. Il marche avec maman. Maman est l'adulte. Ils arrivent au bord. Cédric donne la main. La main est dans la main. Les pieds restent sur le trottoir. Ils restent sur le trottoir en attendant.
+maman|On attend le feu vert.
+narrateur|Cédric sent la main. Il reste près de maman. Le feu est vert.
+maman|Feu vert. On avance avec l'adulte.
+narrateur|Cédric tient la main. Ils marchent ensemble. L'adulte est là.
+enfant-m|Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1495,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Cédric attend avec maman. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1672,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Cédric a donné la main. Il a attendu le feu vert. Maman, l'adulte, était là. Les pieds sont restés sur le trottoir en attendant.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1843,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Cédric serre la main de maman. Ils sentent les fruits.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2010,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2050,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.002-06.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.002-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 enfant-m|Merci maman.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1502,6 +1508,7 @@
           <t>narrateur|Cédric attend avec maman. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1677,6 +1684,7 @@
           <t>narrateur|Cédric a donné la main. Il a attendu le feu vert. Maman, l'adulte, était là. Les pieds sont restés sur le trottoir en attendant.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1848,6 +1856,7 @@
           <t>narrateur|Cédric serre la main de maman. Ils sentent les fruits.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2015,6 +2024,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2033,7 +2043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2057,6 +2067,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2258,6 +2282,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.RUE.002-06.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.002-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cédric attend le feu vert</t>
+          <t>Le tram luisant</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le tram glisse. Nina veut les fraises du marché. Un gant rouge glisse vers la bordure. Elle serre la main, attend le vert. Le trottoir luisant reste.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Cédric va au marché. Il marche avec maman. Maman est l'adulte. Ils arrivent au bord. Cédric donne la main. La main est dans la main. Les pieds restent sur le trottoir. Ils restent sur le trottoir en attendant. On attend le feu vert. Cédric sent la main. Il reste près de maman. Le feu est vert. Feu vert. On avance avec l'adulte. Cédric tient la main. Ils marchent ensemble. L'adulte est là. Merci maman.</t>
+          <t>Le tram glisse sur les rails mouillés. Le trottoir luisant sent la pluie. Une flaque tient le ciel, tout petit. L'air sent le métal et la fraise. Un store rouge claque au marché. Nina vit ici, avec maman. Son manteau fait un bruit de tissu mouillé. Maman, le tram ! Oui. Il file tout doux. On va chercher les fraises ? Oui, maman. En ce moment, Nina enfile un gant rouge. L'autre gant pend, encore vide. Tu mets le second ? Il est un peu grand. Il te tiendra chaud. Maman tend la main. Je prends ta main. Merci, Nina. Elles marchent sur le trottoir luisant. Les pas font un bruit collé. Le tram tinte, plus loin. Il chante. On reste sur le trottoir. Le marché est un peu plus loin. Les fraises sont rouges ? Oui. Bientôt. Le bord du trottoir arrive, tout net. Une ligne blanche marque la bordure. Le second gant glisse vers la bordure. Il est rouge sur le gris luisant. Mon gant ! On reste sur le trottoir. Tu serres ma main ? Nina serre la main. Ses pieds restent sur le trottoir. Le gant s'arrête contre la ligne blanche. Le petit bonhomme est encore rouge. On attend le vert. Nina regarde le feu piéton. Le tram passe, tout long. Les vitres brillent, puis s'en vont. Il est parti. On attend ensemble. Les fraises sentent encore, tout près. Nina sent le sucré dans l'air. Ses doigts restent dans la main. Puis le petit bonhomme devient vert. Feu vert. On avance ensemble. Elles marchent, main dans la main. Le store rouge claque encore. Les fraises sont petites et brillantes. Elles sentent bon ! Tu portes la barquette ? Nina tient la barquette froide.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Cédric va au marché. Il marche avec maman. Maman est l'adulte. Ils arrivent au bord. Cédric donne la main. La main est dans la main. Les pieds restent sur le trottoir. Ils restent sur le trottoir en attendant. Maman dit : on attend le &lt;emphasis level="moderate"&gt;feu&lt;/emphasis&gt; vert. Cédric sent la main. Il reste près de maman. Le feu est vert. Maman dit : feu vert. On avance avec l'adulte. Cédric tient la main. Ils marchent ensemble. L'adulte est là. Cédric dit : merci maman.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le tram glisse sur les rails mouillés. Le trottoir luisant sent la pluie. Une flaque tient le ciel, tout petit. L'air sent le métal et la fraise. Un store rouge claque au marché. Nina vit ici, avec maman. Son manteau fait un bruit de tissu mouillé. Maman, le tram ! Oui. Il file tout doux. On va chercher les fraises ? Oui, maman. En ce moment, Nina enfile un gant rouge. L'autre gant pend, encore vide. Tu mets le second ? Il est un peu grand. Il te tiendra chaud. Maman tend la main. Je prends ta main. Merci, Nina. Elles marchent sur le trottoir luisant. Les pas font un bruit collé. Le tram tinte, plus loin. Il chante. On reste sur le trottoir. Le marché est un peu plus loin. Les fraises sont rouges ? Oui. Bientôt. Le bord du trottoir arrive, tout net. Une ligne blanche marque la bordure. Le second gant glisse vers la bordure. Il est rouge sur le gris luisant. Mon gant ! On reste sur le trottoir. Tu serres ma main ? Nina serre la main. Ses pieds restent sur le trottoir. Le gant s'arrête contre la ligne blanche. Le petit bonhomme est encore rouge. On attend le vert. Nina regarde le feu piéton. Le tram passe, tout long. Les vitres brillent, puis s'en vont. Il est parti. On attend ensemble. Les fraises sentent encore, tout près. Nina sent le sucré dans l'air. Ses doigts restent dans la main. Puis le petit bonhomme devient vert. Feu vert. On avance ensemble. Elles marchent, main dans la main. Le store rouge claque encore. Les fraises sont petites et brillantes. Elles sentent bon ! Tu portes la barquette ? Nina tient la barquette froide.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,15 +1324,71 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Cédric va au marché. Il marche avec maman. Maman est l'adulte. Ils arrivent au bord. Cédric donne la main. La main est dans la main. Les pieds restent sur le trottoir. Ils restent sur le trottoir en attendant.
-maman|On attend le feu vert.
-narrateur|Cédric sent la main. Il reste près de maman. Le feu est vert.
-maman|Feu vert. On avance avec l'adulte.
-narrateur|Cédric tient la main. Ils marchent ensemble. L'adulte est là.
-enfant-m|Merci maman.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le tram glisse sur les rails mouillés.
+narrateur|Le trottoir luisant sent la pluie.
+narrateur|Une flaque tient le ciel, tout petit.
+narrateur|L'air sent le métal et la fraise.
+narrateur|Un store rouge claque au marché.
+narrateur|Nina vit ici, avec maman.
+narrateur|Son manteau fait un bruit de tissu mouillé.
+enfant-f|Maman, le tram !
+maman|Oui.
+maman|Il file tout doux.
+maman|On va chercher les fraises ?
+enfant-f|Oui, maman.
+narrateur|En ce moment, Nina enfile un gant rouge.
+narrateur|L'autre gant pend, encore vide.
+maman|Tu mets le second ?
+enfant-f|Il est un peu grand.
+maman|Il te tiendra chaud.
+narrateur|Maman tend la main.
+enfant-f|Je prends ta main.
+maman|Merci, Nina.
+narrateur|Elles marchent sur le trottoir luisant.
+narrateur|Les pas font un bruit collé.
+narrateur|Le tram tinte, plus loin.
+enfant-f|Il chante.
+maman|On reste sur le trottoir.
+narrateur|Le marché est un peu plus loin.
+enfant-f|Les fraises sont rouges ?
+maman|Oui.
+maman|Bientôt.
+narrateur|Le bord du trottoir arrive, tout net.
+narrateur|Une ligne blanche marque la bordure.
+narrateur|Le second gant glisse vers la bordure.
+narrateur|Il est rouge sur le gris luisant.
+enfant-f|Mon gant !
+maman|On reste sur le trottoir.
+maman|Tu serres ma main ?
+narrateur|Nina serre la main.
+narrateur|Ses pieds restent sur le trottoir.
+narrateur|Le gant s'arrête contre la ligne blanche.
+narrateur|Le petit bonhomme est encore rouge.
+maman|On attend le vert.
+narrateur|Nina regarde le feu piéton.
+narrateur|Le tram passe, tout long.
+narrateur|Les vitres brillent, puis s'en vont.
+enfant-f|Il est parti.
+maman|On attend ensemble.
+narrateur|Les fraises sentent encore, tout près.
+narrateur|Nina sent le sucré dans l'air.
+narrateur|Ses doigts restent dans la main.
+narrateur|Puis le petit bonhomme devient vert.
+maman|Feu vert.
+maman|On avance ensemble.
+narrateur|Elles marchent, main dans la main.
+narrateur|Le store rouge claque encore.
+narrateur|Les fraises sont petites et brillantes.
+enfant-f|Elles sentent bon !
+maman|Tu portes la barquette ?
+narrateur|Nina tient la barquette froide.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>voiture_passe</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1345,12 +1413,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Cédric attend avec maman. Que fait-il ?</t>
+          <t>Nina attend avec maman. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Cédric attend avec maman. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina attend avec maman. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1365,7 +1433,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>feu vert | la main | avec maman | avec l'adulte | attendre</t>
+          <t>feu vert | la main | avec maman | avec papa | avec l'adulte | attendre | le vert</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1380,7 +1448,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il donne la main. Il attend le feu vert. Que fait Cédric ?</t>
+          <t>Elle serre la main. Elle attend le feu vert. Que fait Nina ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1429,7 +1497,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1505,10 +1573,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Cédric attend avec maman. Que fait-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Nina attend avec maman.
+narrateur|Que fait-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1533,12 +1601,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Cédric a donné la main. Il a attendu le feu vert. Maman, l'adulte, était là. Les pieds sont restés sur le trottoir en attendant.</t>
+          <t>Nina a serré la main. Elle a attendu le feu vert. Ses pieds restaient sur le trottoir. Tu as attendu le vert ? Oui, maman. Le gant rouge dort sur la ligne. Les fraises parfument les doigts.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Cédric a donné la main. Il a attendu le &lt;emphasis level="moderate"&gt;feu&lt;/emphasis&gt; vert. Maman, l'adulte, était là. Les pieds sont restés sur le trottoir en attendant.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina a serré la main. Elle a attendu le feu vert. Ses pieds restaient sur le trottoir. Tu as attendu le vert ? Oui, maman. Le gant rouge dort sur la ligne. Les fraises parfument les doigts.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1594,14 +1662,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1681,10 +1749,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Cédric a donné la main. Il a attendu le feu vert. Maman, l'adulte, était là. Les pieds sont restés sur le trottoir en attendant.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nina a serré la main.
+narrateur|Elle a attendu le feu vert.
+narrateur|Ses pieds restaient sur le trottoir.
+maman|Tu as attendu le vert ?
+enfant-f|Oui, maman.
+narrateur|Le gant rouge dort sur la ligne.
+narrateur|Les fraises parfument les doigts.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1709,12 +1782,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Cédric serre la main de maman. Ils sentent les fruits.</t>
+          <t>Elles s'abritent sous le store. Nina pose la barquette contre elle. Une fraise laisse un jus rose. Elle est sucrée. Oui. Tu en manges une ? Nina croque, tout doux. Le jus tache un peu le gant. Le trottoir luisant tremble encore. C'est bon. On ramasse l'autre gant ? Sur le trottoir. Maman le ramasse, tout près du bord. Le tram tinte, déjà loin.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Cédric serre la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de maman. Ils sentent les fruits.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Elles s'abritent sous le store. Nina pose la barquette contre elle. Une fraise laisse un jus rose. Elle est sucrée. Oui. Tu en manges une ? Nina croque, tout doux. Le jus tache un peu le gant. Le trottoir luisant tremble encore. C'est bon. On ramasse l'autre gant ? Sur le trottoir. Maman le ramasse, tout près du bord. Le tram tinte, déjà loin.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1770,14 +1843,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1853,10 +1926,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Cédric serre la main de maman. Ils sentent les fruits.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Elles s'abritent sous le store.
+narrateur|Nina pose la barquette contre elle.
+narrateur|Une fraise laisse un jus rose.
+enfant-f|Elle est sucrée.
+maman|Oui.
+maman|Tu en manges une ?
+narrateur|Nina croque, tout doux.
+narrateur|Le jus tache un peu le gant.
+narrateur|Le trottoir luisant tremble encore.
+enfant-f|C'est bon.
+maman|On ramasse l'autre gant ?
+enfant-f|Sur le trottoir.
+narrateur|Maman le ramasse, tout près du bord.
+narrateur|Le tram tinte, déjà loin.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1881,12 +1966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina lèche un doigt rose. La flaque tient encore un bout de ciel. Les fraises sont à nous. Oui. Le tram file, tout doux, au loin.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina lèche un doigt rose. La flaque tient encore un bout de ciel. Les fraises sont à nous. Oui. Le tram file, tout doux, au loin.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1942,14 +2027,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2021,10 +2106,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Nina lèche un doigt rose.
+narrateur|La flaque tient encore un bout de ciel.
+enfant-f|Les fraises sont à nous.
+maman|Oui.
+narrateur|Le tram file, tout doux, au loin.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2043,7 +2131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2081,6 +2169,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.002-06.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.002-06.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>trajet vers le marché</t>
+          <t>ville après la pluie, tram, marché</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cédric, maman</t>
+          <t>Nina, maman</t>
         </is>
       </c>
     </row>
